--- a/tests/workbooktests/workbooks/test_options.xlsx
+++ b/tests/workbooktests/workbooks/test_options.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D2D96D-C284-4AA5-8F64-83B15B8D03E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA4B6A2-F5C2-4EEF-B839-05CFED5D70DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13530" yWindow="-19245" windowWidth="23175" windowHeight="16410" tabRatio="704" xr2:uid="{CCFA635F-0F53-474D-82D2-FB064D5998FA}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" tabRatio="704" activeTab="7" xr2:uid="{CCFA635F-0F53-474D-82D2-FB064D5998FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Market data" sheetId="1" r:id="rId1"/>
@@ -1058,7 +1058,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00000000"/>
-    <numFmt numFmtId="173" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1142,7 +1142,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B4" t="str" cm="1">
         <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B5" t="str" cm="1">
         <f t="array" ref="B5">_xll.qlFlatForward(B2,0.02)</f>
-        <v>⚡[test_options.xlsx]Market data!R5C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R5C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B7" t="str" cm="1">
         <f t="array" ref="B7">_xll.qlBlackConstantVol(EvaluationDate,"NullCalendar",0.25,"Act/365")</f>
-        <v>⚡[test_options.xlsx]Market data!R7C2BlackVolTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R7C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B10" t="str" cm="1">
         <f t="array" ref="B10">_xll.qlGeneralizedBlackScholesProcess(B9,DividendCurve,DiscountCurve,BlackVolatility)</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R3C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B5" t="str" cm="1">
         <f t="array" ref="B5">_xll.qlEuropeanExercise(B4)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R5C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R5C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1614,7 +1614,7 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G8" s="2" t="str" cm="1">
         <f t="array" ref="G8">_xll.qlTimeGridFromTimes(H8:I8)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R8C7TimeGrid,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R8C7TimeGrid,A</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1658,18 +1658,18 @@
       </c>
       <c r="G10" s="2" t="str" cm="1">
         <f t="array" ref="G10">_xll.qlPiecewiseConstantParameter($H$8:$I$8,H10:J10)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R10C7PiecewiseConstantParameter,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R10C7PiecewiseConstantParameter,A</v>
       </c>
       <c r="H10">
-        <f>$B10</f>
+        <f t="shared" ref="H10:J13" si="0">$B10</f>
         <v>0.39716005835063128</v>
       </c>
       <c r="I10">
-        <f>$B10</f>
+        <f t="shared" si="0"/>
         <v>0.39716005835063128</v>
       </c>
       <c r="J10">
-        <f>$B10</f>
+        <f t="shared" si="0"/>
         <v>0.39716005835063128</v>
       </c>
     </row>
@@ -1692,18 +1692,18 @@
       </c>
       <c r="G11" s="2" t="str" cm="1">
         <f t="array" ref="G11">_xll.qlPiecewiseConstantParameter($H$8:$I$8,H11:J11)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R11C7PiecewiseConstantParameter,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R11C7PiecewiseConstantParameter,A</v>
       </c>
       <c r="H11">
-        <f>$B11</f>
+        <f t="shared" si="0"/>
         <v>7.5903860839074258E-2</v>
       </c>
       <c r="I11">
-        <f>$B11</f>
+        <f t="shared" si="0"/>
         <v>7.5903860839074258E-2</v>
       </c>
       <c r="J11">
-        <f>$B11</f>
+        <f t="shared" si="0"/>
         <v>7.5903860839074258E-2</v>
       </c>
     </row>
@@ -1726,18 +1726,18 @@
       </c>
       <c r="G12" s="2" t="str" cm="1">
         <f t="array" ref="G12">_xll.qlPiecewiseConstantParameter($H$8:$I$8,H12:J12)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R12C7PiecewiseConstantParameter,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R12C7PiecewiseConstantParameter,A</v>
       </c>
       <c r="H12">
-        <f>$B12</f>
+        <f t="shared" si="0"/>
         <v>1.3901714719854346</v>
       </c>
       <c r="I12">
-        <f>$B12</f>
+        <f t="shared" si="0"/>
         <v>1.3901714719854346</v>
       </c>
       <c r="J12">
-        <f>$B12</f>
+        <f t="shared" si="0"/>
         <v>1.3901714719854346</v>
       </c>
     </row>
@@ -1760,18 +1760,18 @@
       </c>
       <c r="G13" s="2" t="str" cm="1">
         <f t="array" ref="G13">_xll.qlPiecewiseConstantParameter($H$8:$I$8,H13:J13)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R13C7PiecewiseConstantParameter,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R13C7PiecewiseConstantParameter,A</v>
       </c>
       <c r="H13">
-        <f>$B13</f>
+        <f t="shared" si="0"/>
         <v>-0.3506856326404631</v>
       </c>
       <c r="I13">
-        <f>$B13</f>
+        <f t="shared" si="0"/>
         <v>-0.3506856326404631</v>
       </c>
       <c r="J13">
-        <f>$B13</f>
+        <f t="shared" si="0"/>
         <v>-0.3506856326404631</v>
       </c>
     </row>
@@ -1789,14 +1789,14 @@
       </c>
       <c r="B15" t="str" cm="1">
         <f t="array" ref="B15">_xll.qlHestonProcess(DiscountCurve,DividendCurve,InitialValueS0,B9,B10,B11,B12,B13,B14)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R15C2HestonProcess,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R15C2HestonProcess,A</v>
       </c>
       <c r="D15" t="s">
         <v>117</v>
       </c>
       <c r="E15" t="str" cm="1">
         <f t="array" ref="E15">_xll.qlHestonModelProcess(B16)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R15C5HestonProcess,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R15C5HestonProcess,A</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B16" t="str" cm="1">
         <f t="array" ref="B16">_xll.qlHestonModel(B15)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R16C2HestonModel,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R16C2HestonModel,A</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B18" t="str" cm="1">
         <f t="array" ref="B18">_xll.qlPiecewiseTimeDependentHestonModel(DiscountCurve,DividendCurve,InitialValueS0,B9,G11,G10,G12,G13,G8)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R18C2PiecewiseTimeDependentHestonModel,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R18C2PiecewiseTimeDependentHestonModel,A</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1951,27 +1951,27 @@
       </c>
       <c r="B33" s="2" t="str" cm="1">
         <f t="array" ref="B33">_xll.qlAnalyticHestonEngine(B16,B26)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R33C2AnalyticHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R33C2AnalyticHestonEngine,A</v>
       </c>
       <c r="C33" s="2" t="str" cm="1">
         <f t="array" ref="C33">_xll.qlAnalyticHestonEngine(B16,,C27,,C29)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R33C3AnalyticHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R33C3AnalyticHestonEngine,A</v>
       </c>
       <c r="D33" s="2" t="str" cm="1">
         <f t="array" ref="D33">_xll.qlAnalyticHestonEngine(B16,,,,,,D31)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R33C4AnalyticHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R33C4AnalyticHestonEngine,A</v>
       </c>
       <c r="E33" s="2" t="str" cm="1">
         <f t="array" ref="E33">_xll.qlAnalyticHestonEngine(B16,,,E28,E29,,E31)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R33C5AnalyticHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R33C5AnalyticHestonEngine,A</v>
       </c>
       <c r="F33" s="2" t="str" cm="1">
         <f t="array" ref="F33">_xll.qlAnalyticHestonEngine(B16,,F27,F28,F29,,F31)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R33C6AnalyticHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R33C6AnalyticHestonEngine,A</v>
       </c>
       <c r="G33" s="2" t="str" cm="1">
         <f t="array" ref="G33">_xll.qlAnalyticHestonEngine(B16,,G27,,,,G31)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R33C7AnalyticHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R33C7AnalyticHestonEngine,A</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1980,27 +1980,27 @@
       </c>
       <c r="B34" s="2" t="str" cm="1">
         <f t="array" ref="B34">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R34C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R34C2VanillaOption,A</v>
       </c>
       <c r="C34" s="2" t="str" cm="1">
         <f t="array" ref="C34">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R34C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R34C3VanillaOption,A</v>
       </c>
       <c r="D34" s="2" t="str" cm="1">
         <f t="array" ref="D34">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R34C4VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R34C4VanillaOption,A</v>
       </c>
       <c r="E34" s="2" t="str" cm="1">
         <f t="array" ref="E34">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R34C5VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R34C5VanillaOption,A</v>
       </c>
       <c r="F34" s="2" t="str" cm="1">
         <f t="array" ref="F34">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R34C6VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R34C6VanillaOption,A</v>
       </c>
       <c r="G34" s="2" t="str" cm="1">
         <f t="array" ref="G34">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R34C7VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R34C7VanillaOption,A</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2088,11 +2088,11 @@
       </c>
       <c r="B42" s="2" t="str" cm="1">
         <f t="array" ref="B42">_xll.qlCOSHestonEngine(B16)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R42C2COSHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R42C2COSHestonEngine,A</v>
       </c>
       <c r="C42" s="2" t="str" cm="1">
         <f t="array" ref="C42">_xll.qlCOSHestonEngine(B16,C40,C41)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R42C3COSHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R42C3COSHestonEngine,A</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2101,11 +2101,11 @@
       </c>
       <c r="B43" s="2" t="str" cm="1">
         <f t="array" ref="B43">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R43C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R43C2VanillaOption,A</v>
       </c>
       <c r="C43" s="2" t="str" cm="1">
         <f t="array" ref="C43">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R43C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R43C3VanillaOption,A</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -2169,11 +2169,11 @@
       </c>
       <c r="B51" s="2" t="str" cm="1">
         <f t="array" ref="B51">_xll.qlExponentialFittingHestonEngine(B16)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R51C2ExponentialFittingHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R51C2ExponentialFittingHestonEngine,A</v>
       </c>
       <c r="C51" s="2" t="str" cm="1">
         <f t="array" ref="C51">_xll.qlExponentialFittingHestonEngine(B16,C48,C49,C50)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R51C3ExponentialFittingHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R51C3ExponentialFittingHestonEngine,A</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -2182,11 +2182,11 @@
       </c>
       <c r="B52" s="2" t="str" cm="1">
         <f t="array" ref="B52">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R52C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R52C2VanillaOption,A</v>
       </c>
       <c r="C52" s="2" t="str" cm="1">
         <f t="array" ref="C52">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R52C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R52C3VanillaOption,A</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -2242,11 +2242,11 @@
       </c>
       <c r="B60" s="2" t="str" cm="1">
         <f t="array" ref="B60">_xll.qlAnalyticPDFHestonEngine(B16)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R60C2AnalyticPDFHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R60C2AnalyticPDFHestonEngine,A</v>
       </c>
       <c r="C60" s="2" t="str" cm="1">
         <f t="array" ref="C60">_xll.qlAnalyticPDFHestonEngine(B16,C58,C59)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R60C3AnalyticPDFHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R60C3AnalyticPDFHestonEngine,A</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -2255,11 +2255,11 @@
       </c>
       <c r="B61" s="2" t="str" cm="1">
         <f t="array" ref="B61">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R61C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R61C2VanillaOption,A</v>
       </c>
       <c r="C61" s="2" t="str" cm="1">
         <f t="array" ref="C61">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R61C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R61C3VanillaOption,A</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -2307,11 +2307,11 @@
       </c>
       <c r="B67" s="2" t="str" cm="1">
         <f t="array" ref="B67">_xll.qlAnalyticHestonForwardEuropeanEngine(B15)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R67C2AnalyticHestonForwardEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R67C2AnalyticHestonForwardEuropeanEngine,A</v>
       </c>
       <c r="C67" s="2" t="str" cm="1">
         <f t="array" ref="C67">_xll.qlAnalyticHestonForwardEuropeanEngine(B15,C66)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R67C3AnalyticHestonForwardEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R67C3AnalyticHestonForwardEuropeanEngine,A</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -2320,11 +2320,11 @@
       </c>
       <c r="B68" s="2" t="str" cm="1">
         <f t="array" ref="B68">_xll.qlForwardVanillaOption(1,EvaluationDate+180,$B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R68C2ForwardVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R68C2ForwardVanillaOption,A</v>
       </c>
       <c r="C68" s="2" t="str" cm="1">
         <f t="array" ref="C68">_xll.qlForwardVanillaOption(1,EvaluationDate+180,$B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R68C3ForwardVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R68C3ForwardVanillaOption,A</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="B73" t="str">
         <f>B18</f>
-        <v>⚡[test_options.xlsx]Heston engines!R18C2PiecewiseTimeDependentHestonModel,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R18C2PiecewiseTimeDependentHestonModel,A</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -2448,27 +2448,27 @@
       </c>
       <c r="B83" s="2" t="str" cm="1">
         <f t="array" ref="B83">_xll.qlAnalyticPTDHestonEngine($B$73,B76)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R83C2AnalyticPTDHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R83C2AnalyticPTDHestonEngine,A</v>
       </c>
       <c r="C83" s="2" t="str" cm="1">
         <f t="array" ref="C83">_xll.qlAnalyticPTDHestonEngine($B$73,,C77,,C79)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R83C3AnalyticPTDHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R83C3AnalyticPTDHestonEngine,A</v>
       </c>
       <c r="D83" s="2" t="str" cm="1">
         <f t="array" ref="D83">_xll.qlAnalyticPTDHestonEngine($B$73,,,,,,D81)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R83C4AnalyticPTDHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R83C4AnalyticPTDHestonEngine,A</v>
       </c>
       <c r="E83" s="2" t="str" cm="1">
         <f t="array" ref="E83">_xll.qlAnalyticPTDHestonEngine($B$73,,,E78,E79,,E81)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R83C5AnalyticPTDHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R83C5AnalyticPTDHestonEngine,A</v>
       </c>
       <c r="F83" s="2" t="str" cm="1">
         <f t="array" ref="F83">_xll.qlAnalyticPTDHestonEngine($B$73,,F77,F78,F79,,F81)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R83C6AnalyticPTDHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R83C6AnalyticPTDHestonEngine,A</v>
       </c>
       <c r="G83" s="12" t="str" cm="1">
         <f t="array" ref="G83">_xll.qlAnalyticPTDHestonEngine($B$73,,G77,,,,G81)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R83C7AnalyticPTDHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R83C7AnalyticPTDHestonEngine,A</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -2477,27 +2477,27 @@
       </c>
       <c r="B84" s="2" t="str" cm="1">
         <f t="array" ref="B84">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R84C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R84C2VanillaOption,A</v>
       </c>
       <c r="C84" s="2" t="str" cm="1">
         <f t="array" ref="C84">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R84C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R84C3VanillaOption,A</v>
       </c>
       <c r="D84" s="2" t="str" cm="1">
         <f t="array" ref="D84">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R84C4VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R84C4VanillaOption,A</v>
       </c>
       <c r="E84" s="2" t="str" cm="1">
         <f t="array" ref="E84">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R84C5VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R84C5VanillaOption,A</v>
       </c>
       <c r="F84" s="2" t="str" cm="1">
         <f t="array" ref="F84">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R84C6VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R84C6VanillaOption,A</v>
       </c>
       <c r="G84" s="2" t="str" cm="1">
         <f t="array" ref="G84">_xll.qlVanillaOption($B$3,$B$5)</f>
-        <v>⚡[test_options.xlsx]Heston engines!R84C7VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Heston engines!R84C7VanillaOption,A</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R3C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R3C2PlainVanillaPayoff,A</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>155</v>
@@ -2629,11 +2629,11 @@
       </c>
       <c r="F4" s="2" t="str" cm="1">
         <f t="array" ref="F4">_xll.qlBinomialVanillaEngine($B$12,E4,$B$11)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R4C6BinomialCRRVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R4C6BinomialCRRVanillaEngine,A</v>
       </c>
       <c r="G4" s="2" t="str" cm="1">
         <f t="array" ref="G4">_xll.qlVanillaOption($B$3,$B$10)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R4C7VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R4C7VanillaOption,A</v>
       </c>
       <c r="H4" cm="1">
         <f t="array" ref="H4">_xll.qlInstrumentNPV(G4,_xll.qlInstrumentSetPricingEngine(G4,F4))</f>
@@ -2653,11 +2653,11 @@
       </c>
       <c r="F5" s="2" t="str" cm="1">
         <f t="array" ref="F5">_xll.qlBinomialVanillaEngine($B$12,E5,$B$11)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R5C6BinomialJRVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R5C6BinomialJRVanillaEngine,A</v>
       </c>
       <c r="G5" s="2" t="str" cm="1">
         <f t="array" ref="G5">_xll.qlVanillaOption($B$3,$B$10)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R5C7VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R5C7VanillaOption,A</v>
       </c>
       <c r="H5" cm="1">
         <f t="array" ref="H5">_xll.qlInstrumentNPV(G5,_xll.qlInstrumentSetPricingEngine(G5,F5))</f>
@@ -2677,11 +2677,11 @@
       </c>
       <c r="F6" s="2" t="str" cm="1">
         <f t="array" ref="F6">_xll.qlBinomialVanillaEngine($B$12,E6,$B$11)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R6C6BinomialEQPVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R6C6BinomialEQPVanillaEngine,A</v>
       </c>
       <c r="G6" s="2" t="str" cm="1">
         <f t="array" ref="G6">_xll.qlVanillaOption($B$3,$B$10)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R6C7VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R6C7VanillaOption,A</v>
       </c>
       <c r="H6" cm="1">
         <f t="array" ref="H6">_xll.qlInstrumentNPV(G6,_xll.qlInstrumentSetPricingEngine(G6,F6))</f>
@@ -2694,18 +2694,18 @@
       </c>
       <c r="B7" t="str" cm="1">
         <f t="array" ref="B7">_xll.qlEuropeanExercise(B6)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R7C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R7C2EuropeanExercise,A</v>
       </c>
       <c r="E7" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="2" t="str" cm="1">
         <f t="array" ref="F7">_xll.qlBinomialVanillaEngine($B$12,E7,$B$11)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R7C6BinomialJ4VanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R7C6BinomialJ4VanillaEngine,A</v>
       </c>
       <c r="G7" s="2" t="str" cm="1">
         <f t="array" ref="G7">_xll.qlVanillaOption($B$3,$B$10)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R7C7VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R7C7VanillaOption,A</v>
       </c>
       <c r="H7" cm="1">
         <f t="array" ref="H7">_xll.qlInstrumentNPV(G7,_xll.qlInstrumentSetPricingEngine(G7,F7))</f>
@@ -2718,18 +2718,18 @@
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xll.qlAmericanExercise(B5,B6)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R8C2AmericanExercise,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R8C2AmericanExercise,A</v>
       </c>
       <c r="E8" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="2" t="str" cm="1">
         <f t="array" ref="F8">_xll.qlBinomialVanillaEngine($B$12,E8,$B$11)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R8C6BinomialLRVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R8C6BinomialLRVanillaEngine,A</v>
       </c>
       <c r="G8" s="2" t="str" cm="1">
         <f t="array" ref="G8">_xll.qlVanillaOption($B$3,$B$10)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R8C7VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R8C7VanillaOption,A</v>
       </c>
       <c r="H8" cm="1">
         <f t="array" ref="H8">_xll.qlInstrumentNPV(G8,_xll.qlInstrumentSetPricingEngine(G8,F8))</f>
@@ -2742,11 +2742,11 @@
       </c>
       <c r="F9" s="2" t="str" cm="1">
         <f t="array" ref="F9">_xll.qlBinomialVanillaEngine($B$12,E9,$B$11)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R9C6BinomialTianVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R9C6BinomialTianVanillaEngine,A</v>
       </c>
       <c r="G9" s="2" t="str" cm="1">
         <f t="array" ref="G9">_xll.qlVanillaOption($B$3,$B$10)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R9C7VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R9C7VanillaOption,A</v>
       </c>
       <c r="H9" cm="1">
         <f t="array" ref="H9">_xll.qlInstrumentNPV(G9,_xll.qlInstrumentSetPricingEngine(G9,F9))</f>
@@ -2759,18 +2759,18 @@
       </c>
       <c r="B10" t="str">
         <f>B8</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R8C2AmericanExercise,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R8C2AmericanExercise,A</v>
       </c>
       <c r="E10" t="s">
         <v>162</v>
       </c>
       <c r="F10" s="2" t="str" cm="1">
         <f t="array" ref="F10">_xll.qlBinomialVanillaEngine($B$12,E10,$B$11)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R10C6BinomialTrigeorgisVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R10C6BinomialTrigeorgisVanillaEngine,A</v>
       </c>
       <c r="G10" s="2" t="str" cm="1">
         <f t="array" ref="G10">_xll.qlVanillaOption($B$3,$B$10)</f>
-        <v>⚡[test_options.xlsx]Binomial tree engine!R10C7VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Binomial tree engine!R10C7VanillaOption,A</v>
       </c>
       <c r="H10" cm="1">
         <f t="array" ref="H10">_xll.qlInstrumentNPV(G10,_xll.qlInstrumentSetPricingEngine(G10,F10))</f>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B12" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
   </sheetData>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R3C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="B7" t="str" cm="1">
         <f t="array" ref="B7">_xll.qlEuropeanExercise(B6)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R7C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R7C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xll.qlAmericanExercise(B5,B6)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R8C2AmericanExercise,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R8C2AmericanExercise,A</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="B9" t="str">
         <f>B8</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R8C2AmericanExercise,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R8C2AmericanExercise,A</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -2910,11 +2910,11 @@
       </c>
       <c r="B14" s="13" t="str" cm="1">
         <f t="array" ref="B14">_xll.qlFixedDividend(B13,B12)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R14C2FixedDividend,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R14C2FixedDividend,A</v>
       </c>
       <c r="C14" s="13" t="str" cm="1">
         <f t="array" ref="C14">_xll.qlFixedDividend(C13,C12)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R14C3FixedDividend,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R14C3FixedDividend,A</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -2952,11 +2952,11 @@
       </c>
       <c r="B20" s="2" t="str" cm="1">
         <f t="array" ref="B20">_xll.qlFdmSchemeDesc()</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R20C2FdmSchemeDesc,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R20C2FdmSchemeDesc,A</v>
       </c>
       <c r="C20" s="2" t="str" cm="1">
         <f t="array" ref="C20">_xll.qlFdmSchemeDesc(C17,C18,C19)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B23" t="str">
         <f>DiscountCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="B24" t="str" cm="1">
         <f t="array" ref="B24">_xll.qlFlatForward(EvaluationDate,0.04)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R24C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R24C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B25" t="str" cm="1">
         <f t="array" ref="B25">_xll.qlBlackConstantVol(EvaluationDate,"NullCalendar",0.15,"Act/365")</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R25C2BlackVolTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R25C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="B28" t="str" cm="1">
         <f t="array" ref="B28">_xll.qlFdmQuantoHelper(B23,B24,B25,B26,B27)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R28C2FdmQuantoHelper,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R28C2FdmQuantoHelper,A</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -3029,11 +3029,11 @@
       </c>
       <c r="B32" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="C32" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="C34" s="2" t="str">
         <f>$B$28</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R28C2FdmQuantoHelper,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R28C2FdmQuantoHelper,A</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="C38" s="2" t="str">
         <f>$C$20</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -3113,11 +3113,11 @@
       </c>
       <c r="B42" s="2" t="str" cm="1">
         <f t="array" ref="B42">_xll.qlFdBlackScholesVanillaEngine(B32)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R42C2FdBlackScholesVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R42C2FdBlackScholesVanillaEngine,A</v>
       </c>
       <c r="C42" s="2" t="str" cm="1">
         <f t="array" ref="C42">_xll.qlFdBlackScholesVanillaEngine(C32,$B$14:$C$14,C34,C35,C36,C37,C38,C39,C40,C41)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R42C3FdBlackScholesVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R42C3FdBlackScholesVanillaEngine,A</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -3126,11 +3126,11 @@
       </c>
       <c r="B43" s="2" t="str" cm="1">
         <f t="array" ref="B43">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R43C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R43C2VanillaOption,A</v>
       </c>
       <c r="C43" s="2" t="str" cm="1">
         <f t="array" ref="C43">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R43C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R43C3VanillaOption,A</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -3159,11 +3159,11 @@
       </c>
       <c r="B48" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="C48" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C53" s="2" t="str">
         <f>$C$20</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -3210,11 +3210,11 @@
       </c>
       <c r="B54" s="2" t="str" cm="1">
         <f t="array" ref="B54">_xll.qlFdBlackScholesShoutEngine(B48)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R54C2FdBlackScholesShoutEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R54C2FdBlackScholesShoutEngine,A</v>
       </c>
       <c r="C54" s="2" t="str" cm="1">
         <f t="array" ref="C54">_xll.qlFdBlackScholesShoutEngine(C48,B14:C14,C50,C51,C52,C53)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R54C3FdBlackScholesShoutEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R54C3FdBlackScholesShoutEngine,A</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -3223,11 +3223,11 @@
       </c>
       <c r="B55" s="2" t="str" cm="1">
         <f t="array" ref="B55">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R55C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R55C2VanillaOption,A</v>
       </c>
       <c r="C55" s="2" t="str" cm="1">
         <f t="array" ref="C55">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R55C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R55C3VanillaOption,A</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -3256,11 +3256,11 @@
       </c>
       <c r="B60" s="2" t="str" cm="1">
         <f t="array" ref="B60">_xll.qlOrnsteinUhlenbeckProcess(0.03,25,100,100)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R60C2OrnsteinUhlenbeckProcess,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R60C2OrnsteinUhlenbeckProcess,A</v>
       </c>
       <c r="C60" s="2" t="str" cm="1">
         <f t="array" ref="C60">_xll.qlOrnsteinUhlenbeckProcess(0.03,25,100,100)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R60C3OrnsteinUhlenbeckProcess,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R60C3OrnsteinUhlenbeckProcess,A</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -3269,11 +3269,11 @@
       </c>
       <c r="B61" s="2" t="str">
         <f>DiscountCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C61" s="2" t="str">
         <f>DiscountCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="C67" s="2" t="str">
         <f>$C$20</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -3328,11 +3328,11 @@
       </c>
       <c r="B68" s="2" t="str" cm="1">
         <f t="array" ref="B68">_xll.qlFdOrnsteinUhlenbeckVanillaEngine(B60,B61)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R68C2FdOrnsteinUhlenbeckVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R68C2FdOrnsteinUhlenbeckVanillaEngine,A</v>
       </c>
       <c r="C68" s="2" t="str" cm="1">
         <f t="array" ref="C68">_xll.qlFdOrnsteinUhlenbeckVanillaEngine(C60,C61,B14:C14,C63,C64,C65,C66,C67)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R68C3FdOrnsteinUhlenbeckVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R68C3FdOrnsteinUhlenbeckVanillaEngine,A</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -3341,11 +3341,11 @@
       </c>
       <c r="B69" s="2" t="str" cm="1">
         <f t="array" ref="B69">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R69C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R69C2VanillaOption,A</v>
       </c>
       <c r="C69" s="2" t="str" cm="1">
         <f t="array" ref="C69">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R69C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R69C3VanillaOption,A</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B82" t="str" cm="1">
         <f t="array" ref="B82">_xll.qlBatesProcess(DiscountCurve,DividendCurve,InitialValueS0,B74,B75,B76,B77,B78,B79,B80,B81)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R82C2BatesProcess,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R82C2BatesProcess,A</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -3452,11 +3452,11 @@
       </c>
       <c r="B85" s="2" t="str" cm="1">
         <f t="array" ref="B85">_xll.qlBatesModel($B$82)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R85C2BatesModel,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R85C2BatesModel,A</v>
       </c>
       <c r="C85" s="2" t="str" cm="1">
         <f t="array" ref="C85">_xll.qlBatesModel($B$82)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R85C3BatesModel,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R85C3BatesModel,A</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="C91" s="2" t="str">
         <f>$C$20</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R20C3FdmSchemeDesc,A</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -3511,11 +3511,11 @@
       </c>
       <c r="B92" s="2" t="str" cm="1">
         <f t="array" ref="B92">_xll.qlFdBatesVanillaEngine(B85)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R92C2FdBatesVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R92C2FdBatesVanillaEngine,A</v>
       </c>
       <c r="C92" s="2" t="str" cm="1">
         <f t="array" ref="C92">_xll.qlFdBatesVanillaEngine(C85,B14:C14,C87,C88,C89,C90,C91)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R92C3FdBatesVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R92C3FdBatesVanillaEngine,A</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -3524,11 +3524,11 @@
       </c>
       <c r="B93" s="2" t="str" cm="1">
         <f t="array" ref="B93">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R93C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R93C2VanillaOption,A</v>
       </c>
       <c r="C93" s="2" t="str" cm="1">
         <f t="array" ref="C93">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R93C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R93C3VanillaOption,A</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="B103" t="str" cm="1">
         <f t="array" ref="B103">_xll.qlHestonProcess(DiscountCurve,DividendCurve,InitialValueS0,B97,B98,B99,B100,B101,B102)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R103C2HestonProcess,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R103C2HestonProcess,A</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -3614,11 +3614,11 @@
       </c>
       <c r="B107" s="2" t="str" cm="1">
         <f t="array" ref="B107">_xll.qlHestonModel($B$103)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R107C2HestonModel,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R107C2HestonModel,A</v>
       </c>
       <c r="C107" s="2" t="str" cm="1">
         <f t="array" ref="C107">_xll.qlHestonModel($B$103)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R107C3HestonModel,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R107C3HestonModel,A</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="C109" s="2" t="str">
         <f>$B$28</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R28C2FdmQuantoHelper,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R28C2FdmQuantoHelper,A</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="C114" s="2" t="str" cm="1">
         <f t="array" ref="C114">_xll.qlFdmSchemeDescByName("Douglas")</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R114C3FdmSchemeDesc,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R114C3FdmSchemeDesc,A</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C115" s="2" t="str" cm="1">
         <f t="array" ref="C115">_xll.qlLocalConstantVol(EvaluationDate,1.1,"Act/365")</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R115C3LocalVolTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R115C3LocalVolTermStructureHandle,A</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -3699,11 +3699,11 @@
       </c>
       <c r="B117" s="2" t="str" cm="1">
         <f t="array" ref="B117">_xll.qlFdHestonVanillaEngine(B107)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R117C2FdHestonVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R117C2FdHestonVanillaEngine,A</v>
       </c>
       <c r="C117" s="2" t="str" cm="1">
         <f t="array" ref="C117">_xll.qlFdHestonVanillaEngine(C107,B14:C14,C109,C110,C111,C112,C113,C114,C115,C116)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R117C3FdHestonVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R117C3FdHestonVanillaEngine,A</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -3712,11 +3712,11 @@
       </c>
       <c r="B118" s="2" t="str" cm="1">
         <f t="array" ref="B118">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R118C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R118C2VanillaOption,A</v>
       </c>
       <c r="C118" s="2" t="str" cm="1">
         <f t="array" ref="C118">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R118C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R118C3VanillaOption,A</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -3778,11 +3778,11 @@
       </c>
       <c r="B126" s="2" t="str">
         <f>DiscountCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C126" s="2" t="str">
         <f>DiscountCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C132" s="2" t="str" cm="1">
         <f t="array" ref="C132">_xll.qlFdmSchemeDescByName("Douglas")</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R132C3FdmSchemeDesc,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R132C3FdmSchemeDesc,A</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -3840,11 +3840,11 @@
       </c>
       <c r="B133" s="2" t="str" cm="1">
         <f t="array" ref="B133">_xll.qlFdCEVVanillaEngine(B123,B124,B125,B126)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R133C2FdCEVVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R133C2FdCEVVanillaEngine,A</v>
       </c>
       <c r="C133" s="2" t="str" cm="1">
         <f t="array" ref="C133">_xll.qlFdCEVVanillaEngine(C123,C124,C125,C126,C127,C128,C129,C130,C131,C132)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R133C3FdCEVVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R133C3FdCEVVanillaEngine,A</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
@@ -3853,11 +3853,11 @@
       </c>
       <c r="B134" s="2" t="str" cm="1">
         <f t="array" ref="B134">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R134C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R134C2VanillaOption,A</v>
       </c>
       <c r="C134" s="2" t="str" cm="1">
         <f t="array" ref="C134">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R134C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R134C3VanillaOption,A</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -3941,11 +3941,11 @@
       </c>
       <c r="B144" s="2" t="str">
         <f>DiscountCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
       <c r="C144" s="2" t="str">
         <f>DiscountCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="C151" s="2" t="str" cm="1">
         <f t="array" ref="C151">_xll.qlFdmSchemeDescByName("Douglas")</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R151C3FdmSchemeDesc,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R151C3FdmSchemeDesc,A</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
@@ -4011,11 +4011,11 @@
       </c>
       <c r="B152" s="2" t="str" cm="1">
         <f t="array" ref="B152">_xll.qlFdSabrVanillaEngine(B139,B140,B141,B142,B143,B144)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R152C2FdSabrVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R152C2FdSabrVanillaEngine,A</v>
       </c>
       <c r="C152" s="2" t="str" cm="1">
         <f t="array" ref="C152">_xll.qlFdSabrVanillaEngine(C139,C140,C141,C142,C143,C144,C145,C146,C147,C148,C149,C150,C151)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R152C3FdSabrVanillaEngine,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R152C3FdSabrVanillaEngine,A</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
@@ -4024,11 +4024,11 @@
       </c>
       <c r="B153" s="2" t="str" cm="1">
         <f t="array" ref="B153">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R153C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R153C2VanillaOption,A</v>
       </c>
       <c r="C153" s="2" t="str" cm="1">
         <f t="array" ref="C153">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Finite Difference engines!R153C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Finite Difference engines!R153C3VanillaOption,A</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R3C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xll.qlEuropeanExercise(B7)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R8C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R8C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B9" t="str" cm="1">
         <f t="array" ref="B9">_xll.qlAmericanExercise(B6,B7)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R9C2AmericanExercise,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R9C2AmericanExercise,A</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -4141,15 +4141,15 @@
       </c>
       <c r="B12" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="C12" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="D12" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -4245,15 +4245,15 @@
       </c>
       <c r="B22" s="2" t="str" cm="1">
         <f t="array" ref="B22">_xll.qlMCEuropeanEngine(B12,B13,B14,,,,B18)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R22C2MCLDEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R22C2MCLDEuropeanEngine,A</v>
       </c>
       <c r="C22" s="2" t="str" cm="1">
         <f t="array" ref="C22">_xll.qlMCEuropeanEngine(C12,C13,,C15,,,,C19)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R22C3MCLDEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R22C3MCLDEuropeanEngine,A</v>
       </c>
       <c r="D22" s="2" t="str" cm="1">
         <f t="array" ref="D22">_xll.qlMCEuropeanEngine(D12,D13,D14,,D16,D17,D18,D19,D20,D21)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R22C4MCLDEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R22C4MCLDEuropeanEngine,A</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -4262,15 +4262,15 @@
       </c>
       <c r="B23" s="2" t="str" cm="1">
         <f t="array" ref="B23">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R23C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R23C2VanillaOption,A</v>
       </c>
       <c r="C23" s="2" t="str" cm="1">
         <f t="array" ref="C23">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R23C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R23C3VanillaOption,A</v>
       </c>
       <c r="D23" s="2" t="str" cm="1">
         <f t="array" ref="D23">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R23C4VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R23C4VanillaOption,A</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="B24" cm="1">
         <f t="array" ref="B24">_xll.qlInstrumentNPV(B23,_xll.qlInstrumentSetPricingEngine(B23,B22))</f>
-        <v>9.0665504040317231</v>
+        <v>8.7097224309098475</v>
       </c>
       <c r="C24" cm="1">
         <f t="array" ref="C24">_xll.qlInstrumentNPV(C23,_xll.qlInstrumentSetPricingEngine(C23,C22))</f>
@@ -4296,15 +4296,15 @@
       </c>
       <c r="B28" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="C28" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="D28" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -4440,15 +4440,15 @@
       </c>
       <c r="B43" s="2" t="str" cm="1">
         <f t="array" ref="B43">_xll.qlMCAmericanEngine(B28,B29,B30,,,,,B34)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R43C2MCLDAmericanEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R43C2MCLDAmericanEngine,A</v>
       </c>
       <c r="C43" s="2" t="str" cm="1">
         <f t="array" ref="C43">_xll.qlMCAmericanEngine(C28,C29,,C31,,,,C35)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R43C3MCLDAmericanEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R43C3MCLDAmericanEngine,A</v>
       </c>
       <c r="D43" s="2" t="str" cm="1">
         <f t="array" ref="D43">_xll.qlMCAmericanEngine(D28,D29,D30,,D32,D33,D34,D34+D35,D36,D37,D38,D39,D40,D41,D42)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R43C4MCLDAmericanEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R43C4MCLDAmericanEngine,A</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -4457,15 +4457,15 @@
       </c>
       <c r="B44" s="2" t="str" cm="1">
         <f t="array" ref="B44">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R44C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R44C2VanillaOption,A</v>
       </c>
       <c r="C44" s="2" t="str" cm="1">
         <f t="array" ref="C44">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R44C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R44C3VanillaOption,A</v>
       </c>
       <c r="D44" s="2" t="str" cm="1">
         <f t="array" ref="D44">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R44C4VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R44C4VanillaOption,A</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="B45" cm="1">
         <f t="array" ref="B45">_xll.qlInstrumentNPV(B44,_xll.qlInstrumentSetPricingEngine(B44,B43))</f>
-        <v>9.1679447489348505</v>
+        <v>9.1847440240848908</v>
       </c>
       <c r="C45" cm="1">
         <f t="array" ref="C45">_xll.qlInstrumentNPV(C44,_xll.qlInstrumentSetPricingEngine(C44,C43))</f>
@@ -4491,15 +4491,15 @@
       </c>
       <c r="B49" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="C49" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="D49" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -4595,15 +4595,15 @@
       </c>
       <c r="B59" t="str" cm="1">
         <f t="array" ref="B59">_xll.qlMCDigitalEngine(B49,B50,B51,,,,B55)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R59C2MCLDDigitalEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R59C2MCLDDigitalEngine,A</v>
       </c>
       <c r="C59" s="2" t="str" cm="1">
         <f t="array" ref="C59">_xll.qlMCDigitalEngine(C49,C50,,C52,,,,C56)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R59C3MCLDDigitalEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R59C3MCLDDigitalEngine,A</v>
       </c>
       <c r="D59" s="2" t="str" cm="1">
         <f t="array" ref="D59">_xll.qlMCDigitalEngine(D49,D50,D51,,D53,D54,D55,D56,D57,D58)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R59C4MCLDDigitalEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R59C4MCLDDigitalEngine,A</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -4612,15 +4612,15 @@
       </c>
       <c r="B60" s="2" t="str" cm="1">
         <f t="array" ref="B60">_xll.qlVanillaOption(_xll.qlCashOrNothingPayoff($B$1,$B$2-20,100),$B$9)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R60C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R60C2VanillaOption,A</v>
       </c>
       <c r="C60" s="2" t="str" cm="1">
         <f t="array" ref="C60">_xll.qlVanillaOption(_xll.qlCashOrNothingPayoff($B$1,$B$2-20,100),$B$9)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R60C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R60C3VanillaOption,A</v>
       </c>
       <c r="D60" s="2" t="str" cm="1">
         <f t="array" ref="D60">_xll.qlVanillaOption(_xll.qlCashOrNothingPayoff($B$1,$B$2-20,100),$B$9)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R60C4VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R60C4VanillaOption,A</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="B61" cm="1">
         <f t="array" ref="B61">_xll.qlInstrumentNPV(B60,_xll.qlInstrumentSetPricingEngine(B60,B59))</f>
-        <v>39.282326157121943</v>
+        <v>38.991871284032172</v>
       </c>
       <c r="C61" cm="1">
         <f t="array" ref="C61">_xll.qlInstrumentNPV(C60,_xll.qlInstrumentSetPricingEngine(C60,C59))</f>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="B70" t="str" cm="1">
         <f t="array" ref="B70">_xll.qlHestonProcess(DiscountCurve,DividendCurve,InitialValueS0,B64,B65,B66,B67,B68,B69)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -4703,15 +4703,15 @@
       </c>
       <c r="B73" s="2" t="str">
         <f>$B$70</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
       </c>
       <c r="C73" s="2" t="str">
         <f>$B$70</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
       </c>
       <c r="D73" s="2" t="str">
         <f>$B$70</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -4799,15 +4799,15 @@
       </c>
       <c r="B82" s="2" t="str" cm="1">
         <f t="array" ref="B82">_xll.qlMCEuropeanHestonEngine(B73,B74,B75,,,B78)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R82C2MCLDEuropeanHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R82C2MCLDEuropeanHestonEngine,A</v>
       </c>
       <c r="C82" s="2" t="str" cm="1">
         <f t="array" ref="C82">_xll.qlMCEuropeanHestonEngine(C73,C74,,C76,,,C79)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R82C3MCLDEuropeanHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R82C3MCLDEuropeanHestonEngine,A</v>
       </c>
       <c r="D82" s="2" t="str" cm="1">
         <f t="array" ref="D82">_xll.qlMCEuropeanHestonEngine(D73,D74,D75,,D77,D78,D79,D80,D81)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R82C4MCLDEuropeanHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R82C4MCLDEuropeanHestonEngine,A</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -4816,15 +4816,15 @@
       </c>
       <c r="B83" s="2" t="str" cm="1">
         <f t="array" ref="B83">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R83C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R83C2VanillaOption,A</v>
       </c>
       <c r="C83" s="2" t="str" cm="1">
         <f t="array" ref="C83">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R83C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R83C3VanillaOption,A</v>
       </c>
       <c r="D83" s="2" t="str" cm="1">
         <f t="array" ref="D83">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R83C4VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R83C4VanillaOption,A</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B84" cm="1">
         <f t="array" ref="B84">_xll.qlInstrumentNPV(B83,_xll.qlInstrumentSetPricingEngine(B83,B82))</f>
-        <v>10.977833767003894</v>
+        <v>11.453484861858684</v>
       </c>
       <c r="C84" cm="1">
         <f t="array" ref="C84">_xll.qlInstrumentNPV(C83,_xll.qlInstrumentSetPricingEngine(C83,C82))</f>
@@ -4850,15 +4850,15 @@
       </c>
       <c r="B88" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="C88" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="D88" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -4954,15 +4954,15 @@
       </c>
       <c r="B98" s="2" t="str" cm="1">
         <f t="array" ref="B98">_xll.qlMCForwardEuropeanBSEngine(B88,B89,B90,,,,B94)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R98C2MCLDForwardEuropeanBSEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R98C2MCLDForwardEuropeanBSEngine,A</v>
       </c>
       <c r="C98" s="2" t="str" cm="1">
         <f t="array" ref="C98">_xll.qlMCForwardEuropeanBSEngine(C88,C89,,C91,,,,C95)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R98C3MCLDForwardEuropeanBSEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R98C3MCLDForwardEuropeanBSEngine,A</v>
       </c>
       <c r="D98" s="2" t="str" cm="1">
         <f t="array" ref="D98">_xll.qlMCForwardEuropeanBSEngine(D88,D89,D90,,D92,D93,D94,D95,D96,D97)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R98C4MCLDForwardEuropeanBSEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R98C4MCLDForwardEuropeanBSEngine,A</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -4971,15 +4971,15 @@
       </c>
       <c r="B99" s="2" t="str" cm="1">
         <f t="array" ref="B99">_xll.qlForwardVanillaOption(1,$B$5,$B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R99C2ForwardVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R99C2ForwardVanillaOption,A</v>
       </c>
       <c r="C99" s="2" t="str" cm="1">
         <f t="array" ref="C99">_xll.qlForwardVanillaOption(1,$B$5,$B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R99C3ForwardVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R99C3ForwardVanillaOption,A</v>
       </c>
       <c r="D99" s="2" t="str" cm="1">
         <f t="array" ref="D99">_xll.qlForwardVanillaOption(1,$B$5,$B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R99C4ForwardVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R99C4ForwardVanillaOption,A</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="B100" cm="1">
         <f t="array" ref="B100">_xll.qlInstrumentNPV(B99,_xll.qlInstrumentSetPricingEngine(B99,B98))</f>
-        <v>6.7089590261824892</v>
+        <v>6.6298105133204537</v>
       </c>
       <c r="C100" cm="1">
         <f t="array" ref="C100">_xll.qlInstrumentNPV(C99,_xll.qlInstrumentSetPricingEngine(C99,C98))</f>
@@ -5005,15 +5005,15 @@
       </c>
       <c r="B104" s="2" t="str">
         <f>$B$70</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
       </c>
       <c r="C104" s="2" t="str">
         <f>$B$70</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
       </c>
       <c r="D104" s="2" t="str">
         <f>$B$70</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R70C2HestonProcess,A</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -5109,15 +5109,15 @@
       </c>
       <c r="B114" s="2" t="str" cm="1">
         <f t="array" ref="B114">_xll.qlMCForwardEuropeanHestonEngine(B104,B105,B106,,,B109)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R114C2MCLDForwardEuropeanHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R114C2MCLDForwardEuropeanHestonEngine,A</v>
       </c>
       <c r="C114" s="2" t="str" cm="1">
         <f t="array" ref="C114">_xll.qlMCForwardEuropeanHestonEngine(C104,C105,,C107,,,C110)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R114C3MCLDForwardEuropeanHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R114C3MCLDForwardEuropeanHestonEngine,A</v>
       </c>
       <c r="D114" s="2" t="str" cm="1">
         <f t="array" ref="D114">_xll.qlMCForwardEuropeanHestonEngine(D104,D105,D106,,D108,D109,D110,D111,D112,D113)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R114C4MCLDForwardEuropeanHestonEngine,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R114C4MCLDForwardEuropeanHestonEngine,A</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -5126,15 +5126,15 @@
       </c>
       <c r="B115" s="2" t="str" cm="1">
         <f t="array" ref="B115">_xll.qlForwardVanillaOption(1,$B$5,$B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R115C2ForwardVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R115C2ForwardVanillaOption,A</v>
       </c>
       <c r="C115" s="2" t="str" cm="1">
         <f t="array" ref="C115">_xll.qlForwardVanillaOption(1,$B$5,$B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R115C3ForwardVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R115C3ForwardVanillaOption,A</v>
       </c>
       <c r="D115" s="2" t="str" cm="1">
         <f t="array" ref="D115">_xll.qlForwardVanillaOption(1,$B$5,$B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Monte Carlo engines!R115C4ForwardVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Monte Carlo engines!R115C4ForwardVanillaOption,A</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B116" cm="1">
         <f t="array" ref="B116">_xll.qlInstrumentNPV(B115,_xll.qlInstrumentSetPricingEngine(B115,B114))</f>
-        <v>4.809576722869906</v>
+        <v>4.7860243594808889</v>
       </c>
       <c r="C116" cm="1">
         <f t="array" ref="C116">_xll.qlInstrumentNPV(C115,_xll.qlInstrumentSetPricingEngine(C115,C114))</f>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
-        <v>⚡[test_options.xlsx]QD engines!R3C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]QD engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xll.qlEuropeanExercise(B7)</f>
-        <v>⚡[test_options.xlsx]QD engines!R8C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]QD engines!R8C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="B9" t="str" cm="1">
         <f t="array" ref="B9">_xll.qlAmericanExercise(B6,B7)</f>
-        <v>⚡[test_options.xlsx]QD engines!R9C2AmericanExercise,A</v>
+        <v>欣[test_options.xlsx]QD engines!R9C2AmericanExercise,A</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -5244,11 +5244,11 @@
       </c>
       <c r="B12" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="C12" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -5289,11 +5289,11 @@
       </c>
       <c r="B17" s="2" t="str" cm="1">
         <f t="array" ref="B17">_xll.qlQdPlusAmericanEngine(B12)</f>
-        <v>⚡[test_options.xlsx]QD engines!R17C2QdPlusAmericanEngine,A</v>
+        <v>欣[test_options.xlsx]QD engines!R17C2QdPlusAmericanEngine,A</v>
       </c>
       <c r="C17" s="2" t="str" cm="1">
         <f t="array" ref="C17">_xll.qlQdPlusAmericanEngine(C12,C13,C14,C15,C16)</f>
-        <v>⚡[test_options.xlsx]QD engines!R17C3QdPlusAmericanEngine,A</v>
+        <v>欣[test_options.xlsx]QD engines!R17C3QdPlusAmericanEngine,A</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -5302,11 +5302,11 @@
       </c>
       <c r="B18" s="2" t="str" cm="1">
         <f t="array" ref="B18">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]QD engines!R18C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]QD engines!R18C2VanillaOption,A</v>
       </c>
       <c r="C18" s="2" t="str" cm="1">
         <f t="array" ref="C18">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]QD engines!R18C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]QD engines!R18C3VanillaOption,A</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -5328,11 +5328,11 @@
       </c>
       <c r="B23" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
       <c r="C23" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -5357,11 +5357,11 @@
       </c>
       <c r="B26" s="2" t="str" cm="1">
         <f t="array" ref="B26">_xll.qlQdFpAmericanEngine(B23)</f>
-        <v>⚡[test_options.xlsx]QD engines!R26C2QdFpAmericanEngine,A</v>
+        <v>欣[test_options.xlsx]QD engines!R26C2QdFpAmericanEngine,A</v>
       </c>
       <c r="C26" s="2" t="str" cm="1">
         <f t="array" ref="C26">_xll.qlQdFpAmericanEngine(C23,C24,C25)</f>
-        <v>⚡[test_options.xlsx]QD engines!R26C3QdFpAmericanEngine,A</v>
+        <v>欣[test_options.xlsx]QD engines!R26C3QdFpAmericanEngine,A</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="B27" s="2" t="str" cm="1">
         <f t="array" ref="B27">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]QD engines!R27C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]QD engines!R27C2VanillaOption,A</v>
       </c>
       <c r="C27" s="2" t="str" cm="1">
         <f t="array" ref="C27">_xll.qlVanillaOption($B$3,$B$9)</f>
-        <v>⚡[test_options.xlsx]QD engines!R27C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]QD engines!R27C3VanillaOption,A</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
-        <v>⚡[test_options.xlsx]Other engines!R3C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Other engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xll.qlEuropeanExercise(B7)</f>
-        <v>⚡[test_options.xlsx]Other engines!R8C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Other engines!R8C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="B9" t="str" cm="1">
         <f t="array" ref="B9">_xll.qlAmericanExercise(B6,B7)</f>
-        <v>⚡[test_options.xlsx]Other engines!R9C2AmericanExercise,A</v>
+        <v>欣[test_options.xlsx]Other engines!R9C2AmericanExercise,A</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B15" t="str">
         <f>DiscountCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="B16" t="str" cm="1">
         <f t="array" ref="B16">_xll.qlAnalyticCEVEngine(B12,B13,B14,B15)</f>
-        <v>⚡[test_options.xlsx]Other engines!R16C2AnalyticCEVEngine,A</v>
+        <v>欣[test_options.xlsx]Other engines!R16C2AnalyticCEVEngine,A</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="B17" s="2" t="str" cm="1">
         <f t="array" ref="B17">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Other engines!R17C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Other engines!R17C2VanillaOption,A</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="B30" t="str" cm="1">
         <f t="array" ref="B30">_xll.qlBatesProcess(DiscountCurve,DividendCurve,InitialValueS0,B22,B23,B24,B25,B26,B27,B28,B29)</f>
-        <v>⚡[test_options.xlsx]Other engines!R30C2BatesProcess,A</v>
+        <v>欣[test_options.xlsx]Other engines!R30C2BatesProcess,A</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -5618,11 +5618,11 @@
       </c>
       <c r="B33" s="2" t="str" cm="1">
         <f t="array" ref="B33">_xll.qlBatesModel($B$30)</f>
-        <v>⚡[test_options.xlsx]Other engines!R33C2BatesModel,A</v>
+        <v>欣[test_options.xlsx]Other engines!R33C2BatesModel,A</v>
       </c>
       <c r="C33" s="2" t="str" cm="1">
         <f t="array" ref="C33">_xll.qlBatesModel($B$30)</f>
-        <v>⚡[test_options.xlsx]Other engines!R33C3BatesModel,A</v>
+        <v>欣[test_options.xlsx]Other engines!R33C3BatesModel,A</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="B37" s="2" t="str" cm="1">
         <f t="array" ref="B37">_xll.qlBatesEngine(B33)</f>
-        <v>⚡[test_options.xlsx]Other engines!R37C2BatesEngine,A</v>
+        <v>欣[test_options.xlsx]Other engines!R37C2BatesEngine,A</v>
       </c>
       <c r="C37" s="2" t="str" cm="1">
         <f t="array" ref="C37">_xll.qlBatesEngine(C33,C34,C35,C36)</f>
-        <v>⚡[test_options.xlsx]Other engines!R37C3BatesEngine,A</v>
+        <v>欣[test_options.xlsx]Other engines!R37C3BatesEngine,A</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -5668,11 +5668,11 @@
       </c>
       <c r="B38" s="2" t="str" cm="1">
         <f t="array" ref="B38">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Other engines!R38C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Other engines!R38C2VanillaOption,A</v>
       </c>
       <c r="C38" s="2" t="str" cm="1">
         <f t="array" ref="C38">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Other engines!R38C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Other engines!R38C3VanillaOption,A</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="B43" t="str">
         <f>DividendCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R5C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R5C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="B44" t="str">
         <f>DiscountCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="B48" t="str" cm="1">
         <f t="array" ref="B48">_xll.qlVarianceGammaProcess(B42,B43,B44,B45,B46,B47)</f>
-        <v>⚡[test_options.xlsx]Other engines!R48C2VarianceGammaProcess,A</v>
+        <v>欣[test_options.xlsx]Other engines!R48C2VarianceGammaProcess,A</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="B50" t="str" cm="1">
         <f t="array" ref="B50">_xll.qlVarianceGammaEngine(B48)</f>
-        <v>⚡[test_options.xlsx]Other engines!R50C2VarianceGammaEngine,A</v>
+        <v>欣[test_options.xlsx]Other engines!R50C2VarianceGammaEngine,A</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B51" s="2" t="str" cm="1">
         <f t="array" ref="B51">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Other engines!R51C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Other engines!R51C2VanillaOption,A</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -5781,11 +5781,11 @@
       </c>
       <c r="B55" s="2" t="str">
         <f>$B$48</f>
-        <v>⚡[test_options.xlsx]Other engines!R48C2VarianceGammaProcess,A</v>
+        <v>欣[test_options.xlsx]Other engines!R48C2VarianceGammaProcess,A</v>
       </c>
       <c r="C55" s="2" t="str">
         <f>$B$48</f>
-        <v>⚡[test_options.xlsx]Other engines!R48C2VarianceGammaProcess,A</v>
+        <v>欣[test_options.xlsx]Other engines!R48C2VarianceGammaProcess,A</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -5803,11 +5803,11 @@
       </c>
       <c r="B57" s="2" t="str" cm="1">
         <f t="array" ref="B57">_xll.qlFFTVarianceGammaEngine(B55)</f>
-        <v>⚡[test_options.xlsx]Other engines!R57C2FFTVarianceGammaEngine,A</v>
+        <v>欣[test_options.xlsx]Other engines!R57C2FFTVarianceGammaEngine,A</v>
       </c>
       <c r="C57" s="2" t="str" cm="1">
         <f t="array" ref="C57">_xll.qlFFTVarianceGammaEngine(C55,C56)</f>
-        <v>⚡[test_options.xlsx]Other engines!R57C3FFTVarianceGammaEngine,A</v>
+        <v>欣[test_options.xlsx]Other engines!R57C3FFTVarianceGammaEngine,A</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -5816,11 +5816,11 @@
       </c>
       <c r="B58" s="2" t="str" cm="1">
         <f t="array" ref="B58">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Other engines!R58C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Other engines!R58C2VanillaOption,A</v>
       </c>
       <c r="C58" s="2" t="str" cm="1">
         <f t="array" ref="C58">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Other engines!R58C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Other engines!R58C3VanillaOption,A</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="B61" t="str">
         <f>DiscountCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="B62" t="str">
         <f>DividendCurve</f>
-        <v>⚡[test_options.xlsx]Market data!R5C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Market data!R5C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B72" t="str" cm="1">
         <f t="array" ref="B72">_xll.qlGJRGARCHProcess(B61,B62,B63,B64,B65,B66,B67,B68,B69,B70,B71)</f>
-        <v>⚡[test_options.xlsx]Other engines!R72C2GJRGARCHProcess,A</v>
+        <v>欣[test_options.xlsx]Other engines!R72C2GJRGARCHProcess,A</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="B74" t="str" cm="1">
         <f t="array" ref="B74">_xll.qlGJRGARCHModel(B72)</f>
-        <v>⚡[test_options.xlsx]Other engines!R74C2GJRGARCHModel,A</v>
+        <v>欣[test_options.xlsx]Other engines!R74C2GJRGARCHModel,A</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="B75" t="str" cm="1">
         <f t="array" ref="B75">_xll.qlAnalyticGJRGARCHEngine(B74)</f>
-        <v>⚡[test_options.xlsx]Other engines!R75C2AnalyticGJRGARCHEngine,A</v>
+        <v>欣[test_options.xlsx]Other engines!R75C2AnalyticGJRGARCHEngine,A</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -5960,16 +5960,16 @@
       </c>
       <c r="B76" s="2" t="str" cm="1">
         <f t="array" ref="B76">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]Other engines!R76C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Other engines!R76C2VanillaOption,A</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>44</v>
       </c>
-      <c r="B77" s="5" t="e" cm="1">
-        <f t="array" ref="B77">_xll.qlInstrumentNPV(B76,_xll.qlInstrumentSetPricingEngine(B76,B75))</f>
-        <v>#N/A</v>
+      <c r="B77" s="5" t="b" cm="1">
+        <f t="array" ref="B77">ISERROR(_xll.qlInstrumentNPV(B76,_xll.qlInstrumentSetPricingEngine(B76,B75)))</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="B4" t="str" cm="1">
         <f t="array" ref="B4">_xll.qlPlainVanillaPayoff(B2,B3)</f>
-        <v>⚡[test_options.xlsx]Calculators!R4C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Calculators!R4C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="B9" t="str" cm="1">
         <f t="array" ref="B9">_xll.qlBlackCalculator(B4,B5,B7,B8)</f>
-        <v>⚡[test_options.xlsx]Calculators!R9C2BlackCalculator,A</v>
+        <v>欣[test_options.xlsx]Calculators!R9C2BlackCalculator,A</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="B35" t="str" cm="1">
         <f t="array" ref="B35">_xll.qlPlainVanillaPayoff(B33,B34)</f>
-        <v>⚡[test_options.xlsx]Calculators!R35C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Calculators!R35C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="B40" t="str" cm="1">
         <f t="array" ref="B40">_xll.qlBachelierCalculator(B35,B36,B38,B39)</f>
-        <v>⚡[test_options.xlsx]Calculators!R40C2BachelierCalculator,A</v>
+        <v>欣[test_options.xlsx]Calculators!R40C2BachelierCalculator,A</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="B6" t="str" cm="1">
         <f t="array" ref="B6">_xll.qlDeltaVolQuote(B2,B3,B4,B5)</f>
-        <v>⚡[test_options.xlsx]DeltaVolQuote!R6C2DeltaVolQuote,A</v>
+        <v>欣[test_options.xlsx]DeltaVolQuote!R6C2DeltaVolQuote,A</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="B13" t="str" cm="1">
         <f t="array" ref="B13">_xll.qlDeltaVolQuoteAtm(B9,B10,B11,B12)</f>
-        <v>⚡[test_options.xlsx]DeltaVolQuote!R13C2DeltaVolQuote,A</v>
+        <v>欣[test_options.xlsx]DeltaVolQuote!R13C2DeltaVolQuote,A</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R3C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xll.qlEuropeanExercise(B7)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R8C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R8C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="B9" t="str" cm="1">
         <f t="array" ref="B9">_xll.qlAmericanExercise(B6,B7)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R9C2AmericanExercise,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R9C2AmericanExercise,A</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -6766,15 +6766,15 @@
       </c>
       <c r="B12" s="2" t="str" cm="1">
         <f t="array" ref="B12">_xll.qlEuropeanOption(B3,B8)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R12C2EuropeanOption,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R12C2EuropeanOption,A</v>
       </c>
       <c r="C12" s="2" t="str" cm="1">
         <f t="array" ref="C12">_xll.qlVanillaOption(B3,B9)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R12C3VanillaOption,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R12C3VanillaOption,A</v>
       </c>
       <c r="D12" s="2" t="str" cm="1">
         <f t="array" ref="D12">_xll.qlForwardVanillaOption(1,B5,B3,B8)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R12C4ForwardVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R12C4ForwardVanillaOption,A</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -6784,15 +6784,15 @@
       </c>
       <c r="B13" s="2" t="str" cm="1">
         <f t="array" ref="B13">_xll.qlAnalyticEuropeanEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R13C2AnalyticEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R13C2AnalyticEuropeanEngine,A</v>
       </c>
       <c r="C13" s="2" t="str" cm="1">
         <f t="array" ref="C13">_xll.qlBaroneAdesiWhaleyApproximationEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R13C3BaroneAdesiWhaleyApproximationEngine,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R13C3BaroneAdesiWhaleyApproximationEngine,A</v>
       </c>
       <c r="D13" s="2" t="str" cm="1">
         <f t="array" ref="D13">_xll.qlForwardEuropeanEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R13C4ForwardEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R13C4ForwardEuropeanEngine,A</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -6840,15 +6840,15 @@
       </c>
       <c r="B18" t="str" cm="1">
         <f t="array" ref="B18">_xll.qlOptionPayoff(B12)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R18C2Payoff,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R18C2Payoff,A</v>
       </c>
       <c r="C18" t="str" cm="1">
         <f t="array" ref="C18">_xll.qlOptionPayoff(C12)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R18C3Payoff,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R18C3Payoff,A</v>
       </c>
       <c r="D18" t="str" cm="1">
         <f t="array" ref="D18">_xll.qlOptionPayoff(D12)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R18C4Payoff,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R18C4Payoff,A</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -6857,15 +6857,15 @@
       </c>
       <c r="B19" t="str" cm="1">
         <f t="array" ref="B19">_xll.qlOptionExercise(B12)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R19C2Exercise,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R19C2Exercise,A</v>
       </c>
       <c r="C19" t="str" cm="1">
         <f t="array" ref="C19">_xll.qlOptionExercise(C12)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R19C3Exercise,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R19C3Exercise,A</v>
       </c>
       <c r="D19" t="str" cm="1">
         <f t="array" ref="D19">_xll.qlOptionExercise(D12)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R19C4Exercise,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R19C4Exercise,A</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -6882,7 +6882,7 @@
         <v>0.55432980411210231</v>
       </c>
       <c r="D22" cm="1">
-        <f t="array" ref="D22">_xll.qlOneAssetOptionDelta(D12)</f>
+        <f t="array" ref="D22">_xll.qlOneAssetOptionDelta(D12,D14)</f>
         <v>7.1837456553616924E-2</v>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
         <v>1.5430227664142152E-2</v>
       </c>
       <c r="D25" cm="1">
-        <f t="array" ref="D25">_xll.qlOneAssetOptionGamma(D12)</f>
+        <f t="array" ref="D25">_xll.qlOneAssetOptionGamma(D12,D14)</f>
         <v>0</v>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
         <v>-5.0703498908926656</v>
       </c>
       <c r="D26" cm="1">
-        <f t="array" ref="D26">_xll.qlOneAssetOptionTheta(D12)</f>
+        <f t="array" ref="D26">_xll.qlOneAssetOptionTheta(D12,D14)</f>
         <v>0.14367491310723376</v>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
         <v>38.575569160355379</v>
       </c>
       <c r="D28" cm="1">
-        <f t="array" ref="D28">_xll.qlOneAssetOptionVega(D12)</f>
+        <f t="array" ref="D28">_xll.qlOneAssetOptionVega(D12,D14)</f>
         <v>27.648221450537704</v>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
         <v>45.23544513574803</v>
       </c>
       <c r="D29" cm="1">
-        <f t="array" ref="D29">_xll.qlOneAssetOptionRho(D12)</f>
+        <f t="array" ref="D29">_xll.qlOneAssetOptionRho(D12,D14)</f>
         <v>23.52246414275961</v>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         <v>-55.432980411210202</v>
       </c>
       <c r="D30" cm="1">
-        <f t="array" ref="D30">_xll.qlOneAssetOptionDividendRho(D12)</f>
+        <f t="array" ref="D30">_xll.qlOneAssetOptionDividendRho(D12,D14)</f>
         <v>-30.706209798121296</v>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="B37" t="str" cm="1">
         <f t="array" ref="B37">_xll.qlIntegralEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]Vanilla &amp; Forward options!R37C2IntegralEngine,A</v>
+        <v>欣[test_options.xlsx]Vanilla &amp; Forward options!R37C2IntegralEngine,A</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R3C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="B5" t="str" cm="1">
         <f t="array" ref="B5">_xll.qlEuropeanExercise(B4)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R5C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R5C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D7" t="str" cm="1">
         <f t="array" ref="D7">_xll.qlFixedDividend(C7,B7)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R7C4FixedDividend,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R7C4FixedDividend,A</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="D8" t="str" cm="1">
         <f t="array" ref="D8">_xll.qlFixedDividend(C8,B8)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R8C4FixedDividend,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R8C4FixedDividend,A</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -7137,11 +7137,11 @@
       </c>
       <c r="B10" s="2" t="str" cm="1">
         <f t="array" ref="B10">_xll.qlEuropeanOption(B3,B5)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R10C2EuropeanOption,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R10C2EuropeanOption,A</v>
       </c>
       <c r="C10" s="2" t="str" cm="1">
         <f t="array" ref="C10">_xll.qlEuropeanOption(B3,B5)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R10C3EuropeanOption,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R10C3EuropeanOption,A</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -7150,11 +7150,11 @@
       </c>
       <c r="B11" s="2" t="str" cm="1">
         <f t="array" ref="B11">_xll.qlAnalyticDividendEuropeanEngine(BlackScholesProcess,D7:D8)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R11C2AnalyticDividendEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R11C2AnalyticDividendEuropeanEngine,A</v>
       </c>
       <c r="C11" s="2" t="str" cm="1">
         <f t="array" ref="C11">_xll.qlAnalyticDividendEuropeanEngine(BlackScholesProcess,D7)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R11C3AnalyticDividendEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R11C3AnalyticDividendEuropeanEngine,A</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -7202,11 +7202,11 @@
       </c>
       <c r="B18" s="2" t="str" cm="1">
         <f t="array" ref="B18">_xll.qlEuropeanOption(B3,B5)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R18C2EuropeanOption,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R18C2EuropeanOption,A</v>
       </c>
       <c r="C18" s="2" t="str" cm="1">
         <f t="array" ref="C18">_xll.qlEuropeanOption(B3,B5)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R18C3EuropeanOption,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R18C3EuropeanOption,A</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -7226,11 +7226,11 @@
       </c>
       <c r="B20" s="2" t="str" cm="1">
         <f t="array" ref="B20">_xll.qlCashDividendEuropeanEngine(BlackScholesProcess,D7:D8,B19)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R20C2CashDividendEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R20C2CashDividendEuropeanEngine,A</v>
       </c>
       <c r="C20" s="2" t="str" cm="1">
         <f t="array" ref="C20">_xll.qlCashDividendEuropeanEngine(BlackScholesProcess,D7,C19)</f>
-        <v>⚡[test_options.xlsx]Cash dividend engines!R20C3CashDividendEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Cash dividend engines!R20C3CashDividendEuropeanEngine,A</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
-        <v>⚡[test_options.xlsx]American option engines!R3C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]American option engines!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="B7" s="1" t="str" cm="1">
         <f t="array" ref="B7">_xll.qlEuropeanExercise(B6)</f>
-        <v>⚡[test_options.xlsx]American option engines!R7C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]American option engines!R7C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xll.qlAmericanExercise(B5,B6)</f>
-        <v>⚡[test_options.xlsx]American option engines!R8C2AmericanExercise,A</v>
+        <v>欣[test_options.xlsx]American option engines!R8C2AmericanExercise,A</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="B10" t="str" cm="1">
         <f t="array" ref="B10">_xll.qlVanillaOption(B3,B7)</f>
-        <v>⚡[test_options.xlsx]American option engines!R10C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]American option engines!R10C2VanillaOption,A</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="B11" t="str" cm="1">
         <f t="array" ref="B11">_xll.qlAnalyticEuropeanEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]American option engines!R11C2AnalyticEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]American option engines!R11C2AnalyticEuropeanEngine,A</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="B15" t="str" cm="1">
         <f t="array" ref="B15">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]American option engines!R15C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]American option engines!R15C2VanillaOption,A</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="B16" t="str" cm="1">
         <f t="array" ref="B16">_xll.qlBaroneAdesiWhaleyApproximationEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]American option engines!R16C2BaroneAdesiWhaleyApproximationEngine,A</v>
+        <v>欣[test_options.xlsx]American option engines!R16C2BaroneAdesiWhaleyApproximationEngine,A</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B20" t="str" cm="1">
         <f t="array" ref="B20">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]American option engines!R20C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]American option engines!R20C2VanillaOption,A</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="B21" t="str" cm="1">
         <f t="array" ref="B21">_xll.qlBjerksundStenslandApproximationEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]American option engines!R21C2BjerksundStenslandApproximationEngine,A</v>
+        <v>欣[test_options.xlsx]American option engines!R21C2BjerksundStenslandApproximationEngine,A</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="B25" t="str" cm="1">
         <f t="array" ref="B25">_xll.qlVanillaOption($B$3,$B$8)</f>
-        <v>⚡[test_options.xlsx]American option engines!R25C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]American option engines!R25C2VanillaOption,A</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B26" t="str" cm="1">
         <f t="array" ref="B26">_xll.qlJuQuadraticApproximationEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]American option engines!R26C2JuQuadraticApproximationEngine,A</v>
+        <v>欣[test_options.xlsx]American option engines!R26C2JuQuadraticApproximationEngine,A</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="B30" t="str" cm="1">
         <f t="array" ref="B30">_xll.qlCashOrNothingPayoff(B1,B2-20,100)</f>
-        <v>⚡[test_options.xlsx]American option engines!R30C2CashOrNothingPayoff,A</v>
+        <v>欣[test_options.xlsx]American option engines!R30C2CashOrNothingPayoff,A</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="B32" t="str" cm="1">
         <f t="array" ref="B32">_xll.qlVanillaOption($B$30,$B$7)</f>
-        <v>⚡[test_options.xlsx]American option engines!R32C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]American option engines!R32C2VanillaOption,A</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="B33" t="str" cm="1">
         <f t="array" ref="B33">_xll.qlAnalyticEuropeanEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]American option engines!R33C2AnalyticEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]American option engines!R33C2AnalyticEuropeanEngine,A</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="B37" t="str" cm="1">
         <f t="array" ref="B37">_xll.qlVanillaOption($B$30,$B$8)</f>
-        <v>⚡[test_options.xlsx]American option engines!R37C2VanillaOption,A</v>
+        <v>欣[test_options.xlsx]American option engines!R37C2VanillaOption,A</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="B38" t="str" cm="1">
         <f t="array" ref="B38">_xll.qlAnalyticDigitalAmericanEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]American option engines!R38C2AnalyticDigitalAmericanEngine,A</v>
+        <v>欣[test_options.xlsx]American option engines!R38C2AnalyticDigitalAmericanEngine,A</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" ref="B3">_xll.qlPlainVanillaPayoff(B1,B2)</f>
-        <v>⚡[test_options.xlsx]Quanto options!R3C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Quanto options!R3C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xll.qlEuropeanExercise(B7)</f>
-        <v>⚡[test_options.xlsx]Quanto options!R8C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Quanto options!R8C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -7661,11 +7661,11 @@
       </c>
       <c r="B11" s="2" t="str" cm="1">
         <f t="array" ref="B11">_xll.qlQuantoVanillaOption(B3,B8)</f>
-        <v>⚡[test_options.xlsx]Quanto options!R11C2QuantoVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Quanto options!R11C2QuantoVanillaOption,A</v>
       </c>
       <c r="C11" s="2" t="str" cm="1">
         <f t="array" ref="C11">_xll.qlQuantoForwardVanillaOption(1,B5,B3,B8)</f>
-        <v>⚡[test_options.xlsx]Quanto options!R11C3QuantoForwardVanillaOption,A</v>
+        <v>欣[test_options.xlsx]Quanto options!R11C3QuantoForwardVanillaOption,A</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B13" t="str" cm="1">
         <f t="array" ref="B13">_xll.qlFlatForward(EvaluationDate,0.04)</f>
-        <v>⚡[test_options.xlsx]Quanto options!R13C2YieldTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Quanto options!R13C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="B14" t="str" cm="1">
         <f t="array" ref="B14">_xll.qlBlackConstantVol(EvaluationDate,"NullCalendar",0.15,"Act/365")</f>
-        <v>⚡[test_options.xlsx]Quanto options!R14C2BlackVolTermStructureHandle,A</v>
+        <v>欣[test_options.xlsx]Quanto options!R14C2BlackVolTermStructureHandle,A</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -7700,11 +7700,11 @@
       </c>
       <c r="B16" s="2" t="str" cm="1">
         <f t="array" ref="B16">_xll.qlQuantoEuropeanEngine(BlackScholesProcess,B13,B14,B15)</f>
-        <v>⚡[test_options.xlsx]Quanto options!R16C2QuantoEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Quanto options!R16C2QuantoEuropeanEngine,A</v>
       </c>
       <c r="C16" t="str" cm="1">
         <f t="array" ref="C16">_xll.qlQuantoForwardEuropeanEngine(BlackScholesProcess,B13,B14,B15)</f>
-        <v>⚡[test_options.xlsx]Quanto options!R16C3QuantoForwardEuropeanEngine,A</v>
+        <v>欣[test_options.xlsx]Quanto options!R16C3QuantoForwardEuropeanEngine,A</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -7728,18 +7728,9 @@
         <f t="array" ref="B18">_xll.qlInstrumentNPV(B11,B17)</f>
         <v>11.878888587119283</v>
       </c>
-      <c r="C18" s="5" t="str" cm="1">
-        <f t="array" ref="C18">_xll.qlInstrumentNPV(C11,C17)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: wrong engine type
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\instruments.py", line 18, in qlInstrumentNPV
-    return instrument.NPV()
-           ~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 16448, in NPV
-    return _QuantLib.Instrument_NPV(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: wrong engine type
-</v>
+      <c r="C18" s="5" cm="1">
+        <f t="array" ref="C18">FIND("RuntimeError: RuntimeError: wrong engine type",_xll.qlInstrumentNPV(C11,C17))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -7752,7 +7743,7 @@
         <v>25</v>
       </c>
       <c r="B21" cm="1">
-        <f t="array" ref="B21">_xll.qlOneAssetOptionDelta(B11)</f>
+        <f t="array" ref="B21">_xll.qlOneAssetOptionDelta(B11,B17)</f>
         <v>0.61562446332249943</v>
       </c>
     </row>
@@ -7771,7 +7762,7 @@
         <v>28</v>
       </c>
       <c r="B24" cm="1">
-        <f t="array" ref="B24">_xll.qlOneAssetOptionGamma(B11)</f>
+        <f t="array" ref="B24">_xll.qlOneAssetOptionGamma(B11,B17)</f>
         <v>1.5479103002523637E-2</v>
       </c>
     </row>
@@ -7780,7 +7771,7 @@
         <v>29</v>
       </c>
       <c r="B25" cm="1">
-        <f t="array" ref="B25">_xll.qlOneAssetOptionTheta(B11)</f>
+        <f t="array" ref="B25">_xll.qlOneAssetOptionTheta(B11,B17)</f>
         <v>-6.8663978260497398</v>
       </c>
     </row>
@@ -7794,7 +7785,7 @@
         <v>31</v>
       </c>
       <c r="B27" cm="1">
-        <f t="array" ref="B27">_xll.qlOneAssetOptionVega(B11)</f>
+        <f t="array" ref="B27">_xll.qlOneAssetOptionVega(B11,B17)</f>
         <v>43.314940981227871</v>
       </c>
     </row>
@@ -7803,7 +7794,7 @@
         <v>32</v>
       </c>
       <c r="B28" cm="1">
-        <f t="array" ref="B28">_xll.qlOneAssetOptionRho(B11)</f>
+        <f t="array" ref="B28">_xll.qlOneAssetOptionRho(B11,B17)</f>
         <v>-11.878888587119285</v>
       </c>
     </row>
@@ -7812,7 +7803,7 @@
         <v>33</v>
       </c>
       <c r="B29" cm="1">
-        <f t="array" ref="B29">_xll.qlOneAssetOptionDividendRho(B11)</f>
+        <f t="array" ref="B29">_xll.qlOneAssetOptionDividendRho(B11,B17)</f>
         <v>-61.562446332249941</v>
       </c>
     </row>
@@ -7831,7 +7822,7 @@
         <v>45</v>
       </c>
       <c r="B33" cm="1">
-        <f t="array" ref="B33">_xll.qlQuantoVanillaOptionQVega(B11)</f>
+        <f t="array" ref="B33">_xll.qlQuantoVanillaOptionQVega(B11,B17)</f>
         <v>7.6953057915312426</v>
       </c>
     </row>
@@ -7840,7 +7831,7 @@
         <v>46</v>
       </c>
       <c r="B34" cm="1">
-        <f t="array" ref="B34">_xll.qlQuantoVanillaOptionQRho(B11)</f>
+        <f t="array" ref="B34">_xll.qlQuantoVanillaOptionQRho(B11,B17)</f>
         <v>61.562446332249941</v>
       </c>
     </row>
@@ -7849,7 +7840,7 @@
         <v>47</v>
       </c>
       <c r="B35" cm="1">
-        <f t="array" ref="B35">_xll.qlQuantoVanillaOptionQLambda(B11)</f>
+        <f t="array" ref="B35">_xll.qlQuantoVanillaOptionQLambda(B11,B17)</f>
         <v>-2.3085917374593725</v>
       </c>
     </row>
@@ -7929,7 +7920,7 @@
       </c>
       <c r="B6" t="str" cm="1">
         <f t="array" ref="B6">_xll.qlEuropeanExercise(B5)</f>
-        <v>⚡[test_options.xlsx]Multi-asset options!R6C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Multi-asset options!R6C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -7938,7 +7929,7 @@
       </c>
       <c r="B7" t="str" cm="1">
         <f t="array" ref="B7">_xll.qlAmericanExercise(B4,B5)</f>
-        <v>⚡[test_options.xlsx]Multi-asset options!R7C2AmericanExercise,A</v>
+        <v>欣[test_options.xlsx]Multi-asset options!R7C2AmericanExercise,A</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -7955,15 +7946,15 @@
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="str" cm="1">
         <f t="array" ref="B10">_xll.qlMargrabeOption(B1,B2,B6)</f>
-        <v>⚡[test_options.xlsx]Multi-asset options!R10C2MargrabeOption,A</v>
+        <v>欣[test_options.xlsx]Multi-asset options!R10C2MargrabeOption,A</v>
       </c>
       <c r="C10" s="2" t="str" cm="1">
         <f t="array" ref="C10">_xll.qlMargrabeOption(B1,B2,B7)</f>
-        <v>⚡[test_options.xlsx]Multi-asset options!R10C3MargrabeOption,A</v>
+        <v>欣[test_options.xlsx]Multi-asset options!R10C3MargrabeOption,A</v>
       </c>
       <c r="D10" s="2" t="str" cm="1">
         <f t="array" ref="D10">_xll.qlTwoAssetCorrelationOption(D3,D1,D2,B6)</f>
-        <v>⚡[test_options.xlsx]Multi-asset options!R10C4TwoAssetCorrelationOption,A</v>
+        <v>欣[test_options.xlsx]Multi-asset options!R10C4TwoAssetCorrelationOption,A</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -7972,7 +7963,7 @@
       </c>
       <c r="B11" s="2" t="str">
         <f>BlackScholesProcess</f>
-        <v>⚡[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Market data!R10C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -7981,7 +7972,7 @@
       </c>
       <c r="B12" s="2" t="str" cm="1">
         <f t="array" ref="B12">_xll.qlGeneralizedBlackScholesProcess(50,DividendCurve,DiscountCurve,BlackVolatility)</f>
-        <v>⚡[test_options.xlsx]Multi-asset options!R12C2GeneralizedBlackScholesProcess,A</v>
+        <v>欣[test_options.xlsx]Multi-asset options!R12C2GeneralizedBlackScholesProcess,A</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -7998,15 +7989,15 @@
       </c>
       <c r="B14" s="2" t="str" cm="1">
         <f t="array" ref="B14">_xll.qlAnalyticEuropeanMargrabeEngine(B11,B12,B13)</f>
-        <v>⚡[test_options.xlsx]Multi-asset options!R14C2AnalyticEuropeanMargrabeEngine,A</v>
+        <v>欣[test_options.xlsx]Multi-asset options!R14C2AnalyticEuropeanMargrabeEngine,A</v>
       </c>
       <c r="C14" s="2" t="str" cm="1">
         <f t="array" ref="C14">_xll.qlAnalyticAmericanMargrabeEngine(B11,B12,B13)</f>
-        <v>⚡[test_options.xlsx]Multi-asset options!R14C3AnalyticAmericanMargrabeEngine,A</v>
+        <v>欣[test_options.xlsx]Multi-asset options!R14C3AnalyticAmericanMargrabeEngine,A</v>
       </c>
       <c r="D14" t="str" cm="1">
         <f t="array" ref="D14">_xll.qlAnalyticTwoAssetCorrelationEngine(B11,B12,B13)</f>
-        <v>⚡[test_options.xlsx]Multi-asset options!R14C4AnalyticTwoAssetCorrelationEngine,A</v>
+        <v>欣[test_options.xlsx]Multi-asset options!R14C4AnalyticTwoAssetCorrelationEngine,A</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -8125,7 +8116,7 @@
       </c>
       <c r="B6" t="str" cm="1">
         <f t="array" ref="B6">_xll.qlPlainVanillaPayoff(B4,B5)</f>
-        <v>⚡[test_options.xlsx]Other options!R6C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Other options!R6C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -8143,7 +8134,7 @@
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xll.qlEuropeanExercise(B7)</f>
-        <v>⚡[test_options.xlsx]Other options!R8C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Other options!R8C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -8173,7 +8164,7 @@
       </c>
       <c r="B12" t="str" cm="1">
         <f t="array" ref="B12">_xll.qlPlainVanillaPayoff(B10,B11)</f>
-        <v>⚡[test_options.xlsx]Other options!R12C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Other options!R12C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -8191,7 +8182,7 @@
       </c>
       <c r="B14" t="str" cm="1">
         <f t="array" ref="B14">_xll.qlEuropeanExercise(B13)</f>
-        <v>⚡[test_options.xlsx]Other options!R14C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Other options!R14C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -8200,7 +8191,7 @@
       </c>
       <c r="B16" t="str" cm="1">
         <f t="array" ref="B16">_xll.qlCompoundOption(B6,B8,B12,B14)</f>
-        <v>⚡[test_options.xlsx]Other options!R16C2CompoundOption,A</v>
+        <v>欣[test_options.xlsx]Other options!R16C2CompoundOption,A</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -8209,7 +8200,7 @@
       </c>
       <c r="B17" t="str" cm="1">
         <f t="array" ref="B17">_xll.qlAnalyticCompoundOptionEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]Other options!R17C2AnalyticCompoundOptionEngine,A</v>
+        <v>欣[test_options.xlsx]Other options!R17C2AnalyticCompoundOptionEngine,A</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -8267,7 +8258,7 @@
       </c>
       <c r="B26" t="str" cm="1">
         <f t="array" ref="B26">_xll.qlEuropeanExercise(B25)</f>
-        <v>⚡[test_options.xlsx]Other options!R26C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Other options!R26C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -8276,7 +8267,7 @@
       </c>
       <c r="B28" t="str" cm="1">
         <f t="array" ref="B28">_xll.qlSimpleChooserOption(B24,B23,B26)</f>
-        <v>⚡[test_options.xlsx]Other options!R28C2SimpleChooserOption,A</v>
+        <v>欣[test_options.xlsx]Other options!R28C2SimpleChooserOption,A</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -8285,7 +8276,7 @@
       </c>
       <c r="B29" t="str" cm="1">
         <f t="array" ref="B29">_xll.qlAnalyticSimpleChooserEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]Other options!R29C2AnalyticSimpleChooserEngine,A</v>
+        <v>欣[test_options.xlsx]Other options!R29C2AnalyticSimpleChooserEngine,A</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -8351,7 +8342,7 @@
       </c>
       <c r="B38" t="str" cm="1">
         <f t="array" ref="B38">_xll.qlEuropeanExercise(B37)</f>
-        <v>⚡[test_options.xlsx]Other options!R38C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Other options!R38C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -8360,7 +8351,7 @@
       </c>
       <c r="B40" t="str" cm="1">
         <f t="array" ref="B40">_xll.qlComplexChooserOption(B36,B34,B35,B38,B38)</f>
-        <v>⚡[test_options.xlsx]Other options!R40C2ComplexChooserOption,A</v>
+        <v>欣[test_options.xlsx]Other options!R40C2ComplexChooserOption,A</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -8369,7 +8360,7 @@
       </c>
       <c r="B41" t="str" cm="1">
         <f t="array" ref="B41">_xll.qlAnalyticComplexChooserEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]Other options!R41C2AnalyticComplexChooserEngine,A</v>
+        <v>欣[test_options.xlsx]Other options!R41C2AnalyticComplexChooserEngine,A</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -8417,7 +8408,7 @@
       </c>
       <c r="B48" t="str" cm="1">
         <f t="array" ref="B48">_xll.qlPlainVanillaPayoff(B46,B47)</f>
-        <v>⚡[test_options.xlsx]Other options!R48C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Other options!R48C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -8435,7 +8426,7 @@
       </c>
       <c r="B50" t="str" cm="1">
         <f t="array" ref="B50">_xll.qlEuropeanExercise(B49)</f>
-        <v>⚡[test_options.xlsx]Other options!R50C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Other options!R50C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -8482,7 +8473,7 @@
       </c>
       <c r="B57" t="str" cm="1">
         <f t="array" ref="B57">_xll.qlHolderExtensibleOption(B52,B53,B54,B55,B48,B50)</f>
-        <v>⚡[test_options.xlsx]Other options!R57C2HolderExtensibleOption,A</v>
+        <v>欣[test_options.xlsx]Other options!R57C2HolderExtensibleOption,A</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -8491,7 +8482,7 @@
       </c>
       <c r="B58" t="str" cm="1">
         <f t="array" ref="B58">_xll.qlAnalyticHolderExtensibleOptionEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]Other options!R58C2AnalyticHolderExtensibleOptionEngine,A</v>
+        <v>欣[test_options.xlsx]Other options!R58C2AnalyticHolderExtensibleOptionEngine,A</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -8539,7 +8530,7 @@
       </c>
       <c r="B65" t="str" cm="1">
         <f t="array" ref="B65">_xll.qlPlainVanillaPayoff(B63,B64)</f>
-        <v>⚡[test_options.xlsx]Other options!R65C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Other options!R65C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -8557,7 +8548,7 @@
       </c>
       <c r="B67" t="str" cm="1">
         <f t="array" ref="B67">_xll.qlEuropeanExercise(B66)</f>
-        <v>⚡[test_options.xlsx]Other options!R67C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Other options!R67C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -8587,7 +8578,7 @@
       </c>
       <c r="B71" t="str" cm="1">
         <f t="array" ref="B71">_xll.qlPlainVanillaPayoff(B69,B70)</f>
-        <v>⚡[test_options.xlsx]Other options!R71C2PlainVanillaPayoff,A</v>
+        <v>欣[test_options.xlsx]Other options!R71C2PlainVanillaPayoff,A</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -8605,7 +8596,7 @@
       </c>
       <c r="B73" t="str" cm="1">
         <f t="array" ref="B73">_xll.qlEuropeanExercise(B72)</f>
-        <v>⚡[test_options.xlsx]Other options!R73C2EuropeanExercise,A</v>
+        <v>欣[test_options.xlsx]Other options!R73C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -8614,7 +8605,7 @@
       </c>
       <c r="B75" t="str" cm="1">
         <f t="array" ref="B75">_xll.qlWriterExtensibleOption(B65,B67,B71,B73)</f>
-        <v>⚡[test_options.xlsx]Other options!R75C2WriterExtensibleOption,A</v>
+        <v>欣[test_options.xlsx]Other options!R75C2WriterExtensibleOption,A</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -8623,7 +8614,7 @@
       </c>
       <c r="B76" t="str" cm="1">
         <f t="array" ref="B76">_xll.qlAnalyticWriterExtensibleOptionEngine(BlackScholesProcess)</f>
-        <v>⚡[test_options.xlsx]Other options!R76C2AnalyticWriterExtensibleOptionEngine,A</v>
+        <v>欣[test_options.xlsx]Other options!R76C2AnalyticWriterExtensibleOptionEngine,A</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
